--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdaa7c99424d545a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8768baee8fa040a8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8768baee8fa040a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1ac94616b6444180"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1ac94616b6444180"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R082b49ac83d64a56"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R082b49ac83d64a56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfb0b37b9d19b4f88"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfb0b37b9d19b4f88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5635e1babd954fa5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5635e1babd954fa5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra701ac6a6e714858"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra701ac6a6e714858"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ree9df57a294e45cc"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ree9df57a294e45cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re15bd46ede1348d3"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re15bd46ede1348d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R87f90e308da5486c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R87f90e308da5486c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7cdbe84195ad425b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7cdbe84195ad425b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc8a874ccd1eb460c"/>
   </x:sheets>
 </x:workbook>
 </file>
